--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -538,17 +538,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£10.00</t>
+          <t>£9.95</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -589,27 +589,27 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -632,7 +632,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -659,17 +659,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£11.30</t>
+          <t>£11.27</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -710,27 +710,27 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -753,7 +753,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -831,27 +831,27 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -874,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>£14.85</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>£14.92</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>£14.92</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -952,27 +952,27 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -995,7 +995,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£18.99</t>
+          <t>£18.90</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>£21.46</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1073,27 +1073,27 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1194,27 +1194,27 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1264,44 +1264,44 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>£20.70</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>£20.70</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>£20.70</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>£23.50</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>£20.93</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>£20.90</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>£20.90</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>£20.90</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>£21.02</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>£23.50</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>£20.93</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>£20.90</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>£21.02</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>£23.50</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>£23.35</t>
@@ -1315,27 +1315,27 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1385,17 +1385,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>£23.99</t>
+          <t>£23.90</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1436,27 +1436,27 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1506,17 +1506,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£25.99</t>
+          <t>£25.90</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1557,27 +1557,27 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1627,17 +1627,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£25.90</t>
+          <t>£25.55</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1678,27 +1678,27 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1748,17 +1748,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>£35.10</t>
+          <t>£33.29</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>£35.10</t>
+          <t>£33.29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>£35.10</t>
+          <t>£33.29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1799,27 +1799,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1920,27 +1920,27 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2041,27 +2041,27 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>£40.39</t>
+          <t>£38.80</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2162,27 +2162,27 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£38.30</t>
+          <t>£38.25</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2283,27 +2283,27 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2501,27 +2501,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>£37.39</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2622,27 +2622,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2743,27 +2743,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2864,27 +2864,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2985,27 +2985,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>£43.70</t>
+          <t>£43.40</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>£44.09</t>
+          <t>£43.79</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3106,27 +3106,27 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£43.85</t>
+          <t>£43.50</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3227,27 +3227,27 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3348,27 +3348,27 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3469,27 +3469,27 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff72c43e9e5+80021]
-	GetHandleVerifier [0x0x7ff72c43ea40+80112]
-	(No symbol) [0x0x7ff72c1c060f]
-	(No symbol) [0x0x7ff72c218854]
-	(No symbol) [0x0x7ff72c218b1c]
-	(No symbol) [0x0x7ff72c26c927]
-	(No symbol) [0x0x7ff72c24126f]
-	(No symbol) [0x0x7ff72c26968a]
-	(No symbol) [0x0x7ff72c241003]
-	(No symbol) [0x0x7ff72c2095d1]
-	(No symbol) [0x0x7ff72c20a3f3]
-	GetHandleVerifier [0x0x7ff72c6fdd8d+2960445]
-	GetHandleVerifier [0x0x7ff72c6f804a+2936570]
-	GetHandleVerifier [0x0x7ff72c718a87+3070263]
-	GetHandleVerifier [0x0x7ff72c4584ce+185214]
-	GetHandleVerifier [0x0x7ff72c45ff1f+216527]
-	GetHandleVerifier [0x0x7ff72c447c24+117460]
-	GetHandleVerifier [0x0x7ff72c447ddf+117903]
-	GetHandleVerifier [0x0x7ff72c42dcb8+11112]
+	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
+	GetHandleVerifier [0x0x7ff777f9ea40+80112]
+	(No symbol) [0x0x7ff777d2060f]
+	(No symbol) [0x0x7ff777d78854]
+	(No symbol) [0x0x7ff777d78b1c]
+	(No symbol) [0x0x7ff777dcc927]
+	(No symbol) [0x0x7ff777da126f]
+	(No symbol) [0x0x7ff777dc968a]
+	(No symbol) [0x0x7ff777da1003]
+	(No symbol) [0x0x7ff777d695d1]
+	(No symbol) [0x0x7ff777d6a3f3]
+	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
+	GetHandleVerifier [0x0x7ff77825804a+2936570]
+	GetHandleVerifier [0x0x7ff778278a87+3070263]
+	GetHandleVerifier [0x0x7ff777fb84ce+185214]
+	GetHandleVerifier [0x0x7ff777fbff1f+216527]
+	GetHandleVerifier [0x0x7ff777fa7c24+117460]
+	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
+	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'text'</t>
+          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>£1407.2</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-10-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -780,7 +780,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£14.60</t>
+          <t>£14.55</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -931,7 +931,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£15.00</t>
+          <t>£14.98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£21.46</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£21.02</t>
+          <t>£20.89</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>£49.32</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>£43.58</t>
+          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£37.39</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff777f9e9e5+80021]
-	GetHandleVerifier [0x0x7ff777f9ea40+80112]
-	(No symbol) [0x0x7ff777d2060f]
-	(No symbol) [0x0x7ff777d78854]
-	(No symbol) [0x0x7ff777d78b1c]
-	(No symbol) [0x0x7ff777dcc927]
-	(No symbol) [0x0x7ff777da126f]
-	(No symbol) [0x0x7ff777dc968a]
-	(No symbol) [0x0x7ff777da1003]
-	(No symbol) [0x0x7ff777d695d1]
-	(No symbol) [0x0x7ff777d6a3f3]
-	GetHandleVerifier [0x0x7ff77825dd8d+2960445]
-	GetHandleVerifier [0x0x7ff77825804a+2936570]
-	GetHandleVerifier [0x0x7ff778278a87+3070263]
-	GetHandleVerifier [0x0x7ff777fb84ce+185214]
-	GetHandleVerifier [0x0x7ff777fbff1f+216527]
-	GetHandleVerifier [0x0x7ff777fa7c24+117460]
-	GetHandleVerifier [0x0x7ff777fa7ddf+117903]
-	GetHandleVerifier [0x0x7ff777f8dcb8+11112]
+	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
+	GetHandleVerifier [0x0x7ff64e72ea40+80112]
+	(No symbol) [0x0x7ff64e4b060f]
+	(No symbol) [0x0x7ff64e508854]
+	(No symbol) [0x0x7ff64e508b1c]
+	(No symbol) [0x0x7ff64e55c927]
+	(No symbol) [0x0x7ff64e53126f]
+	(No symbol) [0x0x7ff64e55968a]
+	(No symbol) [0x0x7ff64e531003]
+	(No symbol) [0x0x7ff64e4f95d1]
+	(No symbol) [0x0x7ff64e4fa3f3]
+	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
+	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
+	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
+	GetHandleVerifier [0x0x7ff64e7484ce+185214]
+	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
+	GetHandleVerifier [0x0x7ff64e737c24+117460]
+	GetHandleVerifier [0x0x7ff64e737ddf+117903]
+	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>

--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_16-10-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£10.08</t>
+          <t>£10.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -583,33 +583,33 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>£9.99</t>
+          <t>£9.94</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -632,7 +632,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -704,33 +704,33 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>£11.27</t>
+          <t>£11.21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -753,7 +753,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£14.71</t>
+          <t>£14.68</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -825,33 +825,33 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>£14.58</t>
+          <t>£14.51</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -874,7 +874,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>£14.92</t>
+          <t>£14.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -946,33 +946,33 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>£14.87</t>
+          <t>£14.80</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -995,7 +995,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -1067,33 +1067,33 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>£18.91</t>
+          <t>£18.82</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£20.82</t>
+          <t>£20.72</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1188,33 +1188,33 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>£20.63</t>
+          <t>£20.53</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1309,33 +1309,33 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>£20.83</t>
+          <t>£20.73</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1430,33 +1430,33 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>£23.91</t>
+          <t>£23.79</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1551,33 +1551,33 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>£25.91</t>
+          <t>£25.78</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1672,33 +1672,33 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>£25.58</t>
+          <t>£25.45</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1721,12 +1721,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>POA or OOS</t>
+          <t>£49.32</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1799,27 +1799,27 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1914,33 +1914,33 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>£31.27</t>
+          <t>£31.11</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -2035,33 +2035,33 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>£39.68</t>
+          <t>£39.48</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -2156,33 +2156,33 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>£38.51</t>
+          <t>£38.32</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£43.58</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2277,33 +2277,33 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>£38.13</t>
+          <t>£37.94</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -2501,27 +2501,27 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2622,27 +2622,27 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2743,27 +2743,27 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2864,27 +2864,27 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2985,27 +2985,27 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3106,27 +3106,27 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>£43.50</t>
+          <t>£43.75</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3227,27 +3227,27 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3348,27 +3348,27 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3469,27 +3469,27 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+  (Session info: chrome=141.0.7390.67); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff64e72e9e5+80021]
-	GetHandleVerifier [0x0x7ff64e72ea40+80112]
-	(No symbol) [0x0x7ff64e4b060f]
-	(No symbol) [0x0x7ff64e508854]
-	(No symbol) [0x0x7ff64e508b1c]
-	(No symbol) [0x0x7ff64e55c927]
-	(No symbol) [0x0x7ff64e53126f]
-	(No symbol) [0x0x7ff64e55968a]
-	(No symbol) [0x0x7ff64e531003]
-	(No symbol) [0x0x7ff64e4f95d1]
-	(No symbol) [0x0x7ff64e4fa3f3]
-	GetHandleVerifier [0x0x7ff64e9edd8d+2960445]
-	GetHandleVerifier [0x0x7ff64e9e804a+2936570]
-	GetHandleVerifier [0x0x7ff64ea08a87+3070263]
-	GetHandleVerifier [0x0x7ff64e7484ce+185214]
-	GetHandleVerifier [0x0x7ff64e74ff1f+216527]
-	GetHandleVerifier [0x0x7ff64e737c24+117460]
-	GetHandleVerifier [0x0x7ff64e737ddf+117903]
-	GetHandleVerifier [0x0x7ff64e71dcb8+11112]
+	GetHandleVerifier [0x0x7ff6d6b5e9e5+80021]
+	GetHandleVerifier [0x0x7ff6d6b5ea40+80112]
+	(No symbol) [0x0x7ff6d68e060f]
+	(No symbol) [0x0x7ff6d6938854]
+	(No symbol) [0x0x7ff6d6938b1c]
+	(No symbol) [0x0x7ff6d698c927]
+	(No symbol) [0x0x7ff6d696126f]
+	(No symbol) [0x0x7ff6d698968a]
+	(No symbol) [0x0x7ff6d6961003]
+	(No symbol) [0x0x7ff6d69295d1]
+	(No symbol) [0x0x7ff6d692a3f3]
+	GetHandleVerifier [0x0x7ff6d6e1dd8d+2960445]
+	GetHandleVerifier [0x0x7ff6d6e1804a+2936570]
+	GetHandleVerifier [0x0x7ff6d6e38a87+3070263]
+	GetHandleVerifier [0x0x7ff6d6b784ce+185214]
+	GetHandleVerifier [0x0x7ff6d6b7ff1f+216527]
+	GetHandleVerifier [0x0x7ff6d6b67c24+117460]
+	GetHandleVerifier [0x0x7ff6d6b67ddf+117903]
+	GetHandleVerifier [0x0x7ff6d6b4dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffc35eae8d7+23]
 	RtlUserThreadStart [0x0x7ffc3674c53c+44]
 </t>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>Error: HTTPSConnectionPool(host='tiffanynacke.org', port=443): Max retries exceeded with url: / (Caused by SSLError(SSLCertVerificationError(1, '[SSL: CERTIFICATE_VERIFY_FAILED] certificate verify failed: unable to get local issuer certificate (_ssl.c:1032)')))</t>
+          <t>Error: 'NoneType' object has no attribute 'text'</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Error: 'NoneType' object has no attribute 'find_all'</t>
+          <t>£1407.2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
